--- a/InputData/elec/RPfFESCC/RPfFESCC Repayment Period for Financed Elec Sector Capital Costs.xlsx
+++ b/InputData/elec/RPfFESCC/RPfFESCC Repayment Period for Financed Elec Sector Capital Costs.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27528"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,13 +10,13 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80EC3107-A379-4815-A725-E40D4B74474C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="RPfFESCC" sheetId="17" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,6 +28,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,47 +39,47 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
+    <t>RPfFESCC Repayment Period for Financed Electricity Sector Capital Costs</t>
+  </si>
+  <si>
     <t>Source:</t>
   </si>
   <si>
+    <t>National Renewable Energy Laboratory</t>
+  </si>
+  <si>
+    <t>Annual Technology Baseline</t>
+  </si>
+  <si>
+    <t>https://atb.nrel.gov/electricity/2023/index</t>
+  </si>
+  <si>
     <t>Notes</t>
   </si>
   <si>
-    <t>RPfFESCC Repayment Period for Financed Electricity Sector Capital Costs</t>
-  </si>
-  <si>
     <t>This variable is used with Vensim's DEPRECIATE STRAIGHTLINE function to spread repayment of electricity sector</t>
   </si>
   <si>
     <t>capital costs over a set number of years.</t>
   </si>
   <si>
+    <t>We use 30 years because this is the default period used in NREL's Annual Electricity Technology Baseline.</t>
+  </si>
+  <si>
+    <t>Unit: years</t>
+  </si>
+  <si>
+    <t>Time Period</t>
+  </si>
+  <si>
     <t>repayment period</t>
-  </si>
-  <si>
-    <t>Unit: years</t>
-  </si>
-  <si>
-    <t>Time Period</t>
-  </si>
-  <si>
-    <t>National Renewable Energy Laboratory</t>
-  </si>
-  <si>
-    <t>Annual Technology Baseline</t>
-  </si>
-  <si>
-    <t>We use 30 years because this is the default period used in NREL's Annual Electricity Technology Baseline.</t>
-  </si>
-  <si>
-    <t>https://atb.nrel.gov/electricity/2023/index</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -457,125 +459,125 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="93" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="B4" s="7">
         <v>2023</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="B5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="B6" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B11" s="2"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B13" s="2"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2">
       <c r="B18" s="2"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2">
       <c r="B23" s="2"/>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2">
       <c r="B27" s="2"/>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
     </row>
@@ -594,23 +596,23 @@
     <tabColor theme="8" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.5703125" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B2" s="3">
         <v>20</v>
@@ -620,4 +622,175 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7abd873f26c83d98889b6bc5171c7cdd">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="295384f30983e71c631053ca9b14fb23" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A115861-DB93-4003-8C6A-FE09BC6DF3DA}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7359C8E-CFDA-47E6-AC47-B81A6784AD86}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7BD61B9-538F-425E-8C3C-AAC8BE560AD1}"/>
 </file>
--- a/InputData/elec/RPfFESCC/RPfFESCC Repayment Period for Financed Elec Sector Capital Costs.xlsx
+++ b/InputData/elec/RPfFESCC/RPfFESCC Repayment Period for Financed Elec Sector Capital Costs.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27528"/>
-  <workbookPr hidePivotFieldList="1"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\elec\RPfFESCC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ananya.Srinivasan\Documents\EPS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80EC3107-A379-4815-A725-E40D4B74474C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{290B7B1C-8355-4097-B749-5BC7D8938EC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{EF131889-7773-4075-A571-54126E254B3D}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="RPfFESCC" sheetId="17" r:id="rId2"/>
+    <sheet name="Miscellaneous" sheetId="3" r:id="rId2"/>
+    <sheet name="RPfFESCC" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
   <si>
     <t>RPfFESCC Repayment Period for Financed Electricity Sector Capital Costs</t>
   </si>
@@ -45,15 +46,6 @@
     <t>Source:</t>
   </si>
   <si>
-    <t>National Renewable Energy Laboratory</t>
-  </si>
-  <si>
-    <t>Annual Technology Baseline</t>
-  </si>
-  <si>
-    <t>https://atb.nrel.gov/electricity/2023/index</t>
-  </si>
-  <si>
     <t>Notes</t>
   </si>
   <si>
@@ -63,48 +55,130 @@
     <t>capital costs over a set number of years.</t>
   </si>
   <si>
-    <t>We use 30 years because this is the default period used in NREL's Annual Electricity Technology Baseline.</t>
+    <t>Central Electricity Regulatory Commission</t>
+  </si>
+  <si>
+    <t>https://www.cercind.gov.in/2025/orders/103-TT-2025.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For India, the repayment period is same as the depreciation period of the asset. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repayment period differs for old and new projects. For existing projects, post-12 years from commencement of </t>
   </si>
   <si>
     <t>Unit: years</t>
   </si>
   <si>
+    <t>repayment period</t>
+  </si>
+  <si>
     <t>Time Period</t>
   </si>
   <si>
-    <t>repayment period</t>
+    <t xml:space="preserve">operation, and for new projects 15 years post operation commencement, repayment is calculated </t>
+  </si>
+  <si>
+    <t>Coal/Lignite based thermal generating station</t>
+  </si>
+  <si>
+    <t>25 years</t>
+  </si>
+  <si>
+    <t>Gas/Liquid fuel based thermal generating station</t>
+  </si>
+  <si>
+    <t>AC and DC sub-station</t>
+  </si>
+  <si>
+    <t>Gas Insulated Substation (GIS)</t>
+  </si>
+  <si>
+    <t>Hydro generating station including pumped storage hydro generating stations</t>
+  </si>
+  <si>
+    <t>40 years</t>
+  </si>
+  <si>
+    <t>years of depreciation (according to Central Electricity Regulation Commission)</t>
+  </si>
+  <si>
+    <t>`</t>
+  </si>
+  <si>
+    <t>using  Straight Line Method. the balance repayment will be equally divided between the remaining</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After referring to the data given in 'Miscellaneous' sheet, this file assumes the repayment period of capital costs for </t>
+  </si>
+  <si>
+    <t>https://cercind.gov.in/regulations/notification-2024.pdf</t>
+  </si>
+  <si>
+    <t>Wind Power Project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biomass power project with Rankine cycle technology </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 years </t>
+  </si>
+  <si>
+    <t>Non-fossil fuel based co-generation project</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 20 years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Small hydro Project </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35 years </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSW and RDF based power project </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'Useful Life'/ Depreciation Period - Non RE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solar PV/ floating solar/ Solar thermal power project </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'Useful Life'/ Depreciation Period - RE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biomass gasifier based power project </t>
+  </si>
+  <si>
+    <t>20 years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biogas based power project </t>
+  </si>
+  <si>
+    <t>plants to be 25 years.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -120,31 +194,35 @@
       <family val="2"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -152,35 +230,138 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyFill="1"/>
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="4">
-    <cellStyle name="Hyperlink" xfId="3" builtinId="8"/>
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Normal 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -206,44 +387,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -271,14 +452,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -306,6 +504,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -367,13 +582,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -382,6 +590,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -446,144 +661,127 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{368E7624-E8BE-48CA-AABC-DC74C8CDF1B4}">
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="93" customWidth="1"/>
+    <col min="1" max="1" width="8.7265625" style="2"/>
+    <col min="2" max="2" width="84.6328125" style="2" customWidth="1"/>
+    <col min="3" max="16384" width="8.7265625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B4" s="3">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B5" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B6" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="B4" s="7">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="B5" t="s">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
-      <c r="B6" s="8" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="2"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="2" t="s">
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="2"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="B18" s="2"/>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="B23" s="2"/>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="B27" s="2"/>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>39</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1" xr:uid="{E264C0C9-8D50-4970-9ED0-F45FFE459EBD}"/>
+    <hyperlink ref="B5" r:id="rId1" xr:uid="{6B9BB6B5-82B6-480F-A3BA-18D6706E564A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -591,51 +789,209 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8AA279E-4463-4946-87ED-B3052716FB44}">
-  <sheetPr>
-    <tabColor theme="8" tint="-0.499984740745262"/>
-  </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1703E31-A775-47DF-859E-FD6CDFDAA489}">
+  <dimension ref="A2:E13"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.5703125" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="1" max="1" width="39.7265625" customWidth="1"/>
+    <col min="4" max="4" width="35.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="5" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="21"/>
+    </row>
+    <row r="3" spans="1:5" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="16"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="17"/>
+    </row>
+    <row r="4" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="10"/>
+      <c r="D4" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="10"/>
+      <c r="D5" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="10"/>
+      <c r="D6" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="D7" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="D2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F20C90CD-B449-4389-91A9-56A7AC0F1C56}">
+  <sheetPr>
+    <tabColor theme="3"/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="28.90625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="10.36328125" style="2" customWidth="1"/>
+    <col min="3" max="16384" width="8.7265625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="8" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="3">
-        <v>20</v>
+      <c r="B2" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="36.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="9"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D12" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7abd873f26c83d98889b6bc5171c7cdd">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="295384f30983e71c631053ca9b14fb23" ns2:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2918bd8377d530163f38b9d795b11f91">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="78da601b2f01cef83512fa5499e996db" ns2:_="">
     <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
     <xsd:element name="properties">
       <xsd:complexType>
@@ -777,6 +1133,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -784,13 +1149,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A115861-DB93-4003-8C6A-FE09BC6DF3DA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CD77BF2-3F48-444B-B4F8-5EE7FEB1715A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7359C8E-CFDA-47E6-AC47-B81A6784AD86}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2145519A-212C-461E-8D10-6ADD2ABC845C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7BD61B9-538F-425E-8C3C-AAC8BE560AD1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6D283EE-A453-4E44-9B1A-6DC9A37B683B}"/>
 </file>